--- a/data/a_Eingangsdaten/Testdaten/Test1/testreihe-Bedarf-konstant_Strom_1Tag.xlsx
+++ b/data/a_Eingangsdaten/Testdaten/Test1/testreihe-Bedarf-konstant_Strom_1Tag.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HansisRasanterRaser\Desktop\UNI\000_DA\git\knEBiD\data\a_Eingangsdaten\Testdaten\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HansisRasanterRaser\Desktop\UNI\000_DA\git\knEBiD\data\a_Eingangsdaten\Testdaten\Test1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38F3D9D-F1BB-4CEE-A7C4-EC33F17D416C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC1E857-F9AA-419C-A763-0DD6C2F7C80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
     <t>Mobilität</t>
   </si>
   <si>
-    <t>Strom [MW]</t>
+    <t>Strom_Gesamt_Bedarf [MW]</t>
   </si>
 </sst>
 </file>
@@ -45,7 +45,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -101,7 +101,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
